--- a/1학년_12반_진로활동정리.xlsx
+++ b/1학년_12반_진로활동정리.xlsx
@@ -30,7 +30,8 @@
     <sheet name="11221 타이압" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="11222 허윤주" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="11223 홍의찬" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="차시 목록·반 현황" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="프로젝트 진행 확인표" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="차시 목록·반 현황" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'11201 김담희'!$4:$4</definedName>
@@ -64,7 +65,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -98,8 +99,25 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <i val="1"/>
+      <color rgb="00595959"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +134,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
         <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -145,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -166,10 +194,53 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
+          <bgColor rgb="00F8CBAD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00D9D9D9"/>
+          <bgColor rgb="00D9D9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -7578,6 +7649,2198 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="5.5" customWidth="1" min="5" max="5"/>
+    <col width="5.5" customWidth="1" min="6" max="6"/>
+    <col width="5.5" customWidth="1" min="7" max="7"/>
+    <col width="5.5" customWidth="1" min="8" max="8"/>
+    <col width="5.5" customWidth="1" min="9" max="9"/>
+    <col width="5.5" customWidth="1" min="10" max="10"/>
+    <col width="5.5" customWidth="1" min="11" max="11"/>
+    <col width="5.5" customWidth="1" min="12" max="12"/>
+    <col width="5.5" customWidth="1" min="13" max="13"/>
+    <col width="5.5" customWidth="1" min="14" max="14"/>
+    <col width="5.5" customWidth="1" min="15" max="15"/>
+    <col width="5.5" customWidth="1" min="16" max="16"/>
+    <col width="5.5" customWidth="1" min="17" max="17"/>
+    <col width="5.5" customWidth="1" min="18" max="18"/>
+    <col width="5.5" customWidth="1" min="19" max="19"/>
+    <col width="5.5" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="8" customWidth="1" min="22" max="22"/>
+    <col width="70" customWidth="1" min="23" max="23"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026학년도 1학년 12반 진로 프로젝트 진행 확인표</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="42" customHeight="1">
+      <c r="A2" s="10" t="inlineStr">
+        <is>
+          <t>※ 제출: ○ 제출 / × 미제출(빈칸 제출도 ○로 표시하고 기록정도 '하')   ※ 기록정도 — 상: 모든 항목을 구체적으로 작성(주제탐구는 자료 3개 이상+요약) / 중: 핵심 항목은 작성했으나 일부 빈칸·자료 부족 / 하: 대부분 빈칸이거나 출처·한 줄만 작성   ※ P-4 이후 칸은 드롭다운으로 직접 입력하면 색이 자동으로 칠해짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>학번</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="inlineStr">
+        <is>
+          <t>트랙</t>
+        </is>
+      </c>
+      <c r="D4" s="11" t="inlineStr">
+        <is>
+          <t>주제 / 도서 / 습관</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="inlineStr">
+        <is>
+          <t>P-1</t>
+        </is>
+      </c>
+      <c r="F4" s="11" t="n"/>
+      <c r="G4" s="11" t="inlineStr">
+        <is>
+          <t>P-2</t>
+        </is>
+      </c>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="inlineStr">
+        <is>
+          <t>P-3</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="inlineStr">
+        <is>
+          <t>P-4</t>
+        </is>
+      </c>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="11" t="inlineStr">
+        <is>
+          <t>P-5</t>
+        </is>
+      </c>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="11" t="inlineStr">
+        <is>
+          <t>P-6</t>
+        </is>
+      </c>
+      <c r="P4" s="11" t="n"/>
+      <c r="Q4" s="11" t="inlineStr">
+        <is>
+          <t>P-7</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="n"/>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>P-8</t>
+        </is>
+      </c>
+      <c r="T4" s="11" t="n"/>
+      <c r="U4" s="11" t="inlineStr">
+        <is>
+          <t>제출
+차시 수</t>
+        </is>
+      </c>
+      <c r="V4" s="11" t="inlineStr">
+        <is>
+          <t>'상'
+차시 수</t>
+        </is>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>간단기록(차시별 흐름 · 지도 포인트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="11" t="n"/>
+      <c r="E5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="F5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="G5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="I5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="N5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="O5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="P5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="Q5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>제출</t>
+        </is>
+      </c>
+      <c r="T5" s="11" t="inlineStr">
+        <is>
+          <t>기록</t>
+        </is>
+      </c>
+      <c r="U5" s="11" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="W5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>11201</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>김담희</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>유치원 교사의 역할과 유아 발달</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+      <c r="R6" s="4" t="n"/>
+      <c r="S6" s="4" t="n"/>
+      <c r="T6" s="4" t="n"/>
+      <c r="U6" s="4">
+        <f>COUNTIF(E6:T6,"○")</f>
+        <v/>
+      </c>
+      <c r="V6" s="4">
+        <f>COUNTIF(E6:T6,"상")</f>
+        <v/>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>P-1 주제 미정·계획 미작성 → P-2 핵심·하위 질문 작성(자료원 1개) → P-3 자료 4개 충실히 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="4" t="n">
+        <v>11202</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>김도아</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>방사선 치료 효과·부작용과 화학적 조절제</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="n"/>
+      <c r="L7" s="4" t="n"/>
+      <c r="M7" s="4" t="n"/>
+      <c r="N7" s="4" t="n"/>
+      <c r="O7" s="4" t="n"/>
+      <c r="P7" s="4" t="n"/>
+      <c r="Q7" s="4" t="n"/>
+      <c r="R7" s="4" t="n"/>
+      <c r="S7" s="4" t="n"/>
+      <c r="T7" s="4" t="n"/>
+      <c r="U7" s="4">
+        <f>COUNTIF(E7:T7,"○")</f>
+        <v/>
+      </c>
+      <c r="V7" s="4">
+        <f>COUNTIF(E7:T7,"상")</f>
+        <v/>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>P-1 관심 분야만 → P-2 매우 구체적 탐구계획 → P-3 출처 4개만 적고 요약 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>11203</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>김서훈</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>한국·핀란드·싱가포르 교육 비교</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="4" t="n"/>
+      <c r="U8" s="4">
+        <f>COUNTIF(E8:T8,"○")</f>
+        <v/>
+      </c>
+      <c r="V8" s="4">
+        <f>COUNTIF(E8:T8,"상")</f>
+        <v/>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>P-1 수학과 일상 → P-2 교육 비교로 주제 변경 → P-3 OECD·NCIC 자료 4개+다음 탐구 메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="4" t="n">
+        <v>11204</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>김지훈</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>스포츠과학부 대학 비교(박상욱과 공동)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
+      <c r="Q9" s="4" t="n"/>
+      <c r="R9" s="4" t="n"/>
+      <c r="S9" s="4" t="n"/>
+      <c r="T9" s="4" t="n"/>
+      <c r="U9" s="4">
+        <f>COUNTIF(E9:T9,"○")</f>
+        <v/>
+      </c>
+      <c r="V9" s="4">
+        <f>COUNTIF(E9:T9,"상")</f>
+        <v/>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>P-1 거의 빈칸 → P-2 핵심 질문만 → P-3 전체 빈칸 / 개별 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>11205</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>김하윤</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>습관형성</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>헤어 디자인 연습(11월 대회 대비)</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n"/>
+      <c r="R10" s="4" t="n"/>
+      <c r="S10" s="4" t="n"/>
+      <c r="T10" s="4" t="n"/>
+      <c r="U10" s="4">
+        <f>COUNTIF(E10:T10,"○")</f>
+        <v/>
+      </c>
+      <c r="V10" s="4">
+        <f>COUNTIF(E10:T10,"상")</f>
+        <v/>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>P-1 습관 주제 정함 → P-2 SMART 목표 미완성 → P-3 실천 0일, 다음 주 주 4회 다짐</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="4" t="n">
+        <v>11206</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>박상욱</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>스포츠과학부 대학 비교(김지훈과 공동)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n"/>
+      <c r="P11" s="4" t="n"/>
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="4" t="n"/>
+      <c r="T11" s="4" t="n"/>
+      <c r="U11" s="4">
+        <f>COUNTIF(E11:T11,"○")</f>
+        <v/>
+      </c>
+      <c r="V11" s="4">
+        <f>COUNTIF(E11:T11,"상")</f>
+        <v/>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>P-1 주제 미기재 → P-2 핵심 질문만 → P-3 체대입시 학원 자료 2개(대학명 없음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>11207</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>박소은</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>진로독서</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>『지속가능한 출판을 위한 출판 편집의 시작』</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+      <c r="M12" s="4" t="n"/>
+      <c r="N12" s="4" t="n"/>
+      <c r="O12" s="4" t="n"/>
+      <c r="P12" s="4" t="n"/>
+      <c r="Q12" s="4" t="n"/>
+      <c r="R12" s="4" t="n"/>
+      <c r="S12" s="4" t="n"/>
+      <c r="T12" s="4" t="n"/>
+      <c r="U12" s="4">
+        <f>COUNTIF(E12:T12,"○")</f>
+        <v/>
+      </c>
+      <c r="V12" s="4">
+        <f>COUNTIF(E12:T12,"상")</f>
+        <v/>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>P-1 출판 편집 도서 계획 → P-2 리뷰 비교 후 도서 선정 → P-3 '편집자 환상' 목차로 현실 점검</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>11208</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>방채원</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>교사의 언어적 상호작용과 유아 말하기 발달</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+      <c r="M13" s="4" t="n"/>
+      <c r="N13" s="4" t="n"/>
+      <c r="O13" s="4" t="n"/>
+      <c r="P13" s="4" t="n"/>
+      <c r="Q13" s="4" t="n"/>
+      <c r="R13" s="4" t="n"/>
+      <c r="S13" s="4" t="n"/>
+      <c r="T13" s="4" t="n"/>
+      <c r="U13" s="4">
+        <f>COUNTIF(E13:T13,"○")</f>
+        <v/>
+      </c>
+      <c r="V13" s="4">
+        <f>COUNTIF(E13:T13,"상")</f>
+        <v/>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>P-1 미제출 → P-2 구체적 탐구계획 → P-3 박사논문 1개 요약(자료 추가 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="4" t="n">
+        <v>11209</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>백주호</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>합기도 강사가 갖춰야 할 덕목(손지훈과 공동)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="n"/>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n"/>
+      <c r="P14" s="4" t="n"/>
+      <c r="Q14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="n"/>
+      <c r="T14" s="4" t="n"/>
+      <c r="U14" s="4">
+        <f>COUNTIF(E14:T14,"○")</f>
+        <v/>
+      </c>
+      <c r="V14" s="4">
+        <f>COUNTIF(E14:T14,"상")</f>
+        <v/>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>P-1 달리기 관련 → P-2 합기도 강사 덕목 → P-3 지도자 태도 기사 2개 / 필체 판독 어려움</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="4" t="n">
+        <v>11210</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>변준기</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>시대에 따른 음악 스타일의 변화</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+      <c r="M15" s="4" t="n"/>
+      <c r="N15" s="4" t="n"/>
+      <c r="O15" s="4" t="n"/>
+      <c r="P15" s="4" t="n"/>
+      <c r="Q15" s="4" t="n"/>
+      <c r="R15" s="4" t="n"/>
+      <c r="S15" s="4" t="n"/>
+      <c r="T15" s="4" t="n"/>
+      <c r="U15" s="4">
+        <f>COUNTIF(E15:T15,"○")</f>
+        <v/>
+      </c>
+      <c r="V15" s="4">
+        <f>COUNTIF(E15:T15,"상")</f>
+        <v/>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>P-1 음악 스타일 변화 → P-2 미제출 → P-3 서태지와 아이들 기사 1개 / 탐구 질문 보충 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="4" t="n">
+        <v>11211</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>손지훈</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>스포츠 강사의 덕목과 역량(백주호와 공동)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+      <c r="M16" s="4" t="n"/>
+      <c r="N16" s="4" t="n"/>
+      <c r="O16" s="4" t="n"/>
+      <c r="P16" s="4" t="n"/>
+      <c r="Q16" s="4" t="n"/>
+      <c r="R16" s="4" t="n"/>
+      <c r="S16" s="4" t="n"/>
+      <c r="T16" s="4" t="n"/>
+      <c r="U16" s="4">
+        <f>COUNTIF(E16:T16,"○")</f>
+        <v/>
+      </c>
+      <c r="V16" s="4">
+        <f>COUNTIF(E16:T16,"상")</f>
+        <v/>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>P-1 조리 관련 → P-2 스포츠 강사로 변경 → P-3 자료 4개 고르게 수집</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="4" t="n">
+        <v>11212</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>심민주</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>영미 텍스트 번역의 문화적 등가성·문화번역</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+      <c r="M17" s="4" t="n"/>
+      <c r="N17" s="4" t="n"/>
+      <c r="O17" s="4" t="n"/>
+      <c r="P17" s="4" t="n"/>
+      <c r="Q17" s="4" t="n"/>
+      <c r="R17" s="4" t="n"/>
+      <c r="S17" s="4" t="n"/>
+      <c r="T17" s="4" t="n"/>
+      <c r="U17" s="4">
+        <f>COUNTIF(E17:T17,"○")</f>
+        <v/>
+      </c>
+      <c r="V17" s="4">
+        <f>COUNTIF(E17:T17,"상")</f>
+        <v/>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>P-1 미제출 → P-2 매우 구체적 계획 → P-3 이론서·AI 번역 실험·번역본 비교 5개+보고서 구성(반 최고 수준)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="4" t="n">
+        <v>11213</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>안정연</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>습관형성</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>하루 그림 1장 완성(일러스트)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
+      <c r="U18" s="4">
+        <f>COUNTIF(E18:T18,"○")</f>
+        <v/>
+      </c>
+      <c r="V18" s="4">
+        <f>COUNTIF(E18:T18,"상")</f>
+        <v/>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>P-1 거의 빈칸 → P-2 SMART 목표 구체적 → P-3 실천 1일(시작일 착각한 듯)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="4" t="n">
+        <v>11214</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>엄태훈</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>수의사와 사육사 비교</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+      <c r="M19" s="4" t="n"/>
+      <c r="N19" s="4" t="n"/>
+      <c r="O19" s="4" t="n"/>
+      <c r="P19" s="4" t="n"/>
+      <c r="Q19" s="4" t="n"/>
+      <c r="R19" s="4" t="n"/>
+      <c r="S19" s="4" t="n"/>
+      <c r="T19" s="4" t="n"/>
+      <c r="U19" s="4">
+        <f>COUNTIF(E19:T19,"○")</f>
+        <v/>
+      </c>
+      <c r="V19" s="4">
+        <f>COUNTIF(E19:T19,"상")</f>
+        <v/>
+      </c>
+      <c r="W19" s="5" t="inlineStr">
+        <is>
+          <t>P-1 반려동물 수(짝과 공동) → P-2 수의사·사육사 비교 → P-3 연봉·근무 여건·학과 자료 3개</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="4" t="n">
+        <v>11215</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>윤도영</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>숏폼·알고리즘이 청소년에게 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+      <c r="M20" s="4" t="n"/>
+      <c r="N20" s="4" t="n"/>
+      <c r="O20" s="4" t="n"/>
+      <c r="P20" s="4" t="n"/>
+      <c r="Q20" s="4" t="n"/>
+      <c r="R20" s="4" t="n"/>
+      <c r="S20" s="4" t="n"/>
+      <c r="T20" s="4" t="n"/>
+      <c r="U20" s="4">
+        <f>COUNTIF(E20:T20,"○")</f>
+        <v/>
+      </c>
+      <c r="V20" s="4">
+        <f>COUNTIF(E20:T20,"상")</f>
+        <v/>
+      </c>
+      <c r="W20" s="5" t="inlineStr">
+        <is>
+          <t>P-1 방송·유튜브 → P-2 예시와 비슷한 주제 → P-3 실태조사·학술논문 3개로 뒷받침</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="4" t="n">
+        <v>11216</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>이봉희</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>마약 범죄와 경찰의 역할</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="n"/>
+      <c r="U21" s="4">
+        <f>COUNTIF(E21:T21,"○")</f>
+        <v/>
+      </c>
+      <c r="V21" s="4">
+        <f>COUNTIF(E21:T21,"상")</f>
+        <v/>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
+          <t>P-1 구체적 계획 → P-2 마약 정의·범죄 변화 → P-3 대검찰청 자료 1개</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="4" t="n">
+        <v>11217</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>이우주</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>빛으로 물체·색을 인식하는 과정</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+      <c r="Q22" s="4" t="n"/>
+      <c r="R22" s="4" t="n"/>
+      <c r="S22" s="4" t="n"/>
+      <c r="T22" s="4" t="n"/>
+      <c r="U22" s="4">
+        <f>COUNTIF(E22:T22,"○")</f>
+        <v/>
+      </c>
+      <c r="V22" s="4">
+        <f>COUNTIF(E22:T22,"상")</f>
+        <v/>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>P-1·P-2 구체적 → P-3 전체 빈칸 / 결석·사정 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="4" t="n">
+        <v>11218</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>이름확인필요</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>진로독서</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>회계 관련 도서(제목 미기재)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+      <c r="Q23" s="4" t="n"/>
+      <c r="R23" s="4" t="n"/>
+      <c r="S23" s="4" t="n"/>
+      <c r="T23" s="4" t="n"/>
+      <c r="U23" s="4">
+        <f>COUNTIF(E23:T23,"○")</f>
+        <v/>
+      </c>
+      <c r="V23" s="4">
+        <f>COUNTIF(E23:T23,"상")</f>
+        <v/>
+      </c>
+      <c r="W23" s="5" t="inlineStr">
+        <is>
+          <t>P-1 도서 미정 → P-2 회계 도서 선정 → P-3 독서 전 활동 한 줄씩 / 이름 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="4" t="n">
+        <v>11219</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>정은혜</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>(미정)</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>(활동지 없음)</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+      <c r="Q24" s="4" t="n"/>
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="n"/>
+      <c r="T24" s="4" t="n"/>
+      <c r="U24" s="4">
+        <f>COUNTIF(E24:T24,"○")</f>
+        <v/>
+      </c>
+      <c r="V24" s="4">
+        <f>COUNTIF(E24:T24,"상")</f>
+        <v/>
+      </c>
+      <c r="W24" s="5" t="inlineStr">
+        <is>
+          <t>P-1~P-3 모두 미제출 / 결석·미제출 확인 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="4" t="n">
+        <v>11220</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>최나은</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>습관형성</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>경제 뉴스 읽는 습관</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>×</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+      <c r="Q25" s="4" t="n"/>
+      <c r="R25" s="4" t="n"/>
+      <c r="S25" s="4" t="n"/>
+      <c r="T25" s="4" t="n"/>
+      <c r="U25" s="4">
+        <f>COUNTIF(E25:T25,"○")</f>
+        <v/>
+      </c>
+      <c r="V25" s="4">
+        <f>COUNTIF(E25:T25,"상")</f>
+        <v/>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>P-1 구체적 계획 → P-2 미제출 → P-3 월 1회 기록(질 높음), 꾸준함 격려 필요</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="4" t="n">
+        <v>11221</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>타이압</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>가격 전략과 소비자 구매 행동(홍의찬과 공동)</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+      <c r="Q26" s="4" t="n"/>
+      <c r="R26" s="4" t="n"/>
+      <c r="S26" s="4" t="n"/>
+      <c r="T26" s="4" t="n"/>
+      <c r="U26" s="4">
+        <f>COUNTIF(E26:T26,"○")</f>
+        <v/>
+      </c>
+      <c r="V26" s="4">
+        <f>COUNTIF(E26:T26,"상")</f>
+        <v/>
+      </c>
+      <c r="W26" s="5" t="inlineStr">
+        <is>
+          <t>P-1 주제 미정 → P-2 핵심 질문만 → P-3 DBpia 논문 2개 요약</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="4" t="n">
+        <v>11222</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>허윤주</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>미용사가 개인의 삶과 사회에 미치는 영향</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+      <c r="Q27" s="4" t="n"/>
+      <c r="R27" s="4" t="n"/>
+      <c r="S27" s="4" t="n"/>
+      <c r="T27" s="4" t="n"/>
+      <c r="U27" s="4">
+        <f>COUNTIF(E27:T27,"○")</f>
+        <v/>
+      </c>
+      <c r="V27" s="4">
+        <f>COUNTIF(E27:T27,"상")</f>
+        <v/>
+      </c>
+      <c r="W27" s="5" t="inlineStr">
+        <is>
+          <t>P-1 AI 시대 헤어 디자이너 → P-2 구체적 계획 → P-3 자료 4개+메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="4" t="n">
+        <v>11223</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>홍의찬</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>주제탐구</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>가격 전략과 소비자 구매 행동(타이압과 공동)</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>○</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
+      <c r="Q28" s="4" t="n"/>
+      <c r="R28" s="4" t="n"/>
+      <c r="S28" s="4" t="n"/>
+      <c r="T28" s="4" t="n"/>
+      <c r="U28" s="4">
+        <f>COUNTIF(E28:T28,"○")</f>
+        <v/>
+      </c>
+      <c r="V28" s="4">
+        <f>COUNTIF(E28:T28,"상")</f>
+        <v/>
+      </c>
+      <c r="W28" s="5" t="inlineStr">
+        <is>
+          <t>P-1 트랙 미체크 → P-2 핵심 질문만 → P-3 블로그 자료 2개(공신력 보완 필요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>제출 인원(○)</t>
+        </is>
+      </c>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12">
+        <f>IF(COUNTA(E6:E28)=0,"",COUNTIF(E6:E28,"○"))</f>
+        <v/>
+      </c>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12">
+        <f>IF(COUNTA(G6:G28)=0,"",COUNTIF(G6:G28,"○"))</f>
+        <v/>
+      </c>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12">
+        <f>IF(COUNTA(I6:I28)=0,"",COUNTIF(I6:I28,"○"))</f>
+        <v/>
+      </c>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12">
+        <f>IF(COUNTA(K6:K28)=0,"",COUNTIF(K6:K28,"○"))</f>
+        <v/>
+      </c>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12">
+        <f>IF(COUNTA(M6:M28)=0,"",COUNTIF(M6:M28,"○"))</f>
+        <v/>
+      </c>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12">
+        <f>IF(COUNTA(O6:O28)=0,"",COUNTIF(O6:O28,"○"))</f>
+        <v/>
+      </c>
+      <c r="P30" s="12" t="n"/>
+      <c r="Q30" s="12">
+        <f>IF(COUNTA(Q6:Q28)=0,"",COUNTIF(Q6:Q28,"○"))</f>
+        <v/>
+      </c>
+      <c r="R30" s="12" t="n"/>
+      <c r="S30" s="12">
+        <f>IF(COUNTA(S6:S28)=0,"",COUNTIF(S6:S28,"○"))</f>
+        <v/>
+      </c>
+      <c r="T30" s="12" t="n"/>
+      <c r="U30" s="12" t="n"/>
+      <c r="V30" s="12" t="n"/>
+      <c r="W30" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>미제출(×)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12">
+        <f>IF(COUNTA(E6:E28)=0,"",COUNTIF(E6:E28,"×"))</f>
+        <v/>
+      </c>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12">
+        <f>IF(COUNTA(G6:G28)=0,"",COUNTIF(G6:G28,"×"))</f>
+        <v/>
+      </c>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12">
+        <f>IF(COUNTA(I6:I28)=0,"",COUNTIF(I6:I28,"×"))</f>
+        <v/>
+      </c>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12">
+        <f>IF(COUNTA(K6:K28)=0,"",COUNTIF(K6:K28,"×"))</f>
+        <v/>
+      </c>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12">
+        <f>IF(COUNTA(M6:M28)=0,"",COUNTIF(M6:M28,"×"))</f>
+        <v/>
+      </c>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12">
+        <f>IF(COUNTA(O6:O28)=0,"",COUNTIF(O6:O28,"×"))</f>
+        <v/>
+      </c>
+      <c r="P31" s="12" t="n"/>
+      <c r="Q31" s="12">
+        <f>IF(COUNTA(Q6:Q28)=0,"",COUNTIF(Q6:Q28,"×"))</f>
+        <v/>
+      </c>
+      <c r="R31" s="12" t="n"/>
+      <c r="S31" s="12">
+        <f>IF(COUNTA(S6:S28)=0,"",COUNTIF(S6:S28,"×"))</f>
+        <v/>
+      </c>
+      <c r="T31" s="12" t="n"/>
+      <c r="U31" s="12" t="n"/>
+      <c r="V31" s="12" t="n"/>
+      <c r="W31" s="12" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12">
+        <f>IF(COUNTA(F6:F28)=0,"",COUNTIF(F6:F28,"상"))</f>
+        <v/>
+      </c>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12">
+        <f>IF(COUNTA(H6:H28)=0,"",COUNTIF(H6:H28,"상"))</f>
+        <v/>
+      </c>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12">
+        <f>IF(COUNTA(J6:J28)=0,"",COUNTIF(J6:J28,"상"))</f>
+        <v/>
+      </c>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12">
+        <f>IF(COUNTA(L6:L28)=0,"",COUNTIF(L6:L28,"상"))</f>
+        <v/>
+      </c>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12">
+        <f>IF(COUNTA(N6:N28)=0,"",COUNTIF(N6:N28,"상"))</f>
+        <v/>
+      </c>
+      <c r="O32" s="12" t="n"/>
+      <c r="P32" s="12">
+        <f>IF(COUNTA(P6:P28)=0,"",COUNTIF(P6:P28,"상"))</f>
+        <v/>
+      </c>
+      <c r="Q32" s="12" t="n"/>
+      <c r="R32" s="12">
+        <f>IF(COUNTA(R6:R28)=0,"",COUNTIF(R6:R28,"상"))</f>
+        <v/>
+      </c>
+      <c r="S32" s="12" t="n"/>
+      <c r="T32" s="12">
+        <f>IF(COUNTA(T6:T28)=0,"",COUNTIF(T6:T28,"상"))</f>
+        <v/>
+      </c>
+      <c r="U32" s="12" t="n"/>
+      <c r="V32" s="12" t="n"/>
+      <c r="W32" s="12" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>중</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12">
+        <f>IF(COUNTA(F6:F28)=0,"",COUNTIF(F6:F28,"중"))</f>
+        <v/>
+      </c>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12">
+        <f>IF(COUNTA(H6:H28)=0,"",COUNTIF(H6:H28,"중"))</f>
+        <v/>
+      </c>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12">
+        <f>IF(COUNTA(J6:J28)=0,"",COUNTIF(J6:J28,"중"))</f>
+        <v/>
+      </c>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12">
+        <f>IF(COUNTA(L6:L28)=0,"",COUNTIF(L6:L28,"중"))</f>
+        <v/>
+      </c>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12">
+        <f>IF(COUNTA(N6:N28)=0,"",COUNTIF(N6:N28,"중"))</f>
+        <v/>
+      </c>
+      <c r="O33" s="12" t="n"/>
+      <c r="P33" s="12">
+        <f>IF(COUNTA(P6:P28)=0,"",COUNTIF(P6:P28,"중"))</f>
+        <v/>
+      </c>
+      <c r="Q33" s="12" t="n"/>
+      <c r="R33" s="12">
+        <f>IF(COUNTA(R6:R28)=0,"",COUNTIF(R6:R28,"중"))</f>
+        <v/>
+      </c>
+      <c r="S33" s="12" t="n"/>
+      <c r="T33" s="12">
+        <f>IF(COUNTA(T6:T28)=0,"",COUNTIF(T6:T28,"중"))</f>
+        <v/>
+      </c>
+      <c r="U33" s="12" t="n"/>
+      <c r="V33" s="12" t="n"/>
+      <c r="W33" s="12" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12">
+        <f>IF(COUNTA(F6:F28)=0,"",COUNTIF(F6:F28,"하"))</f>
+        <v/>
+      </c>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12">
+        <f>IF(COUNTA(H6:H28)=0,"",COUNTIF(H6:H28,"하"))</f>
+        <v/>
+      </c>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12">
+        <f>IF(COUNTA(J6:J28)=0,"",COUNTIF(J6:J28,"하"))</f>
+        <v/>
+      </c>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12">
+        <f>IF(COUNTA(L6:L28)=0,"",COUNTIF(L6:L28,"하"))</f>
+        <v/>
+      </c>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12">
+        <f>IF(COUNTA(N6:N28)=0,"",COUNTIF(N6:N28,"하"))</f>
+        <v/>
+      </c>
+      <c r="O34" s="12" t="n"/>
+      <c r="P34" s="12">
+        <f>IF(COUNTA(P6:P28)=0,"",COUNTIF(P6:P28,"하"))</f>
+        <v/>
+      </c>
+      <c r="Q34" s="12" t="n"/>
+      <c r="R34" s="12">
+        <f>IF(COUNTA(R6:R28)=0,"",COUNTIF(R6:R28,"하"))</f>
+        <v/>
+      </c>
+      <c r="S34" s="12" t="n"/>
+      <c r="T34" s="12">
+        <f>IF(COUNTA(T6:T28)=0,"",COUNTIF(T6:T28,"하"))</f>
+        <v/>
+      </c>
+      <c r="U34" s="12" t="n"/>
+      <c r="V34" s="12" t="n"/>
+      <c r="W34" s="12" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="V4:V5"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="U4:U5"/>
+    <mergeCell ref="A2:W2"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="W4:W5"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="S4:T4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E6:T28">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"상"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"중"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"하"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"×"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="E6:E28 G6:G28 I6:I28 K6:K28 M6:M28 O6:O28 Q6:Q28 S6:S28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"○,×"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F6:F28 H6:H28 J6:J28 L6:L28 N6:N28 P6:P28 R6:R28 T6:T28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"상,중,하"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -7599,7 +9862,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -7939,7 +10201,6 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
@@ -8707,7 +10968,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
@@ -9447,7 +11707,6 @@
         </is>
       </c>
     </row>
-    <row r="70"/>
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
